--- a/tests/fixtures/08_price_list/data-export-control.xlsx
+++ b/tests/fixtures/08_price_list/data-export-control.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -571,353 +571,354 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>prod.code</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>prod.name</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>prod.unit</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>prod.price</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>EL0001</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>USB-C Hub 7-port</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>49.99</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>EL0002</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Wireless Keyboard</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>EL0003</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>HD Webcam 1080p</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>55.5</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>prod.code</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>prod.name</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>prod.unit</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>prod.price</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>CA0001</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>HDMI 2.0 2m cable</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>9.99</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>CA0002</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>USB-C to USB-A 1m</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G13" s="7" t="n">
         <v>6.49</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>CA0003</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>DisplayPort 1.4 2m</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>12.99</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>CA0004</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Ethernet Cat6 5m</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>8.75</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>prod.code</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>prod.name</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>prod.unit</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>prod.price</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>ST0001</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>SSD 1TB 2.5"</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>ST0002</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>NVMe SSD 500GB</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G19" s="7" t="n">
         <v>65</v>
       </c>
     </row>
